--- a/sim/balance-workbook.xlsx
+++ b/sim/balance-workbook.xlsx
@@ -14521,7 +14521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Null is thick here — ailments bite harder</t>
+          <t xml:space="preserve">the Null is thick here — damage over time bites harder</t>
         </is>
       </c>
       <c r="C6" s="2">
